--- a/important_mails_2026-03-26.xlsx
+++ b/important_mails_2026-03-26.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -500,21 +500,117 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
+          <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (kpCypnMqWe)</t>
+          <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
+ votre compte vendeur Amazon</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon Services.
+ We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
+ Note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. If that is the case, we will continue to charge your card as often as every 24 hours until the remaining balance in your Amazon seller account is paid in full.
+ You can also use the Make a Payment feature to repay the balance you owe. For details, go to seller Help, and search for “Make a Payment.”
+ You can view your payment activity at any time by logging in to your seller account and going to your Payments Report.
+ Thank you for selling on Amazon.ca.
+ Amazon Services
+ *****
+ Bonjour d’Amazon Services,
+ Nous avons débité votre carte bancaire (Visa) pour CDN$ 44.65 pour le règlement du solde de votre compte vendeur.
+ Le montant débité sur votre carte bancaire peut être inférieur au montant total impayé si vous disposez d'une limite de crédit imposée par votre banque. Nous continuerons d'essayer de débiter votre carte bancaire toutes les 24 heures jusqu'à ce que le solde restant de votre compte soit e</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Action Required: Website Suppressed ASINs</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
+We recommend you submit the required documents to un-suppress your ASIN and activate your listings.
+Here is a sample of your suppressed ASINs:
+B0D7SKQ6GC, B0FCDRNTT8
+You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
+https://sellercentral.amazon.com/fixyourproducts/drafts
+To upload the required documents or to appeal to un-suppressed an ASIN, please follow these instructions  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
+https://sellercentral.amazon.com/performance/account/health/compliance-request
+If you need further help, please raise a case via contact us. - https://sellercentral.amazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (kpCypnMqWe)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -534,39 +630,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -592,39 +688,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -640,39 +736,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -693,88 +789,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 03/19/26 15:38 WET, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 74,59.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éxit</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -789,39 +836,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -840,40 +887,40 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -892,39 +939,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -934,39 +981,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -984,39 +1031,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -1032,39 +1079,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1079,39 +1126,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -1126,39 +1173,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -1179,40 +1226,40 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -1227,39 +1274,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -1280,39 +1327,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -1345,58 +1392,10 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
-Dear there,
-Thank you for being a valued member of the Amazon Multichannel Fulfillment (MCF) and Buy with Prime community. We are reaching again out to make sure you have seen that starting in April 2026, MCF and Buy with Prime will introduce two updates to how orders are packaged and shipped in the United States:
-Packing slips will no longer be included by default.
-Items already certified for the Ships in Product Packaging (SIPP) program on Amazon.com will ship without an Amazon overbox by default.
-In addition, eligible MCF and Buy with Prime SIPP shipments will receive a discount. See the SIPP for MCF help content for details.
-https://www2.amazonsupplychain.com/e/949422/ence-external-GVCFXDFYNCTFLTTQ/61b9cx/1372255659/h/xX050fPuJyuSx_HuFPheaHfGRXD19yafaiWekQ5-4Gg
-Packing slips will no longer be included by default.
-Items already certified for the Ships in Product Packaging (SIPP) program on Amazon.com will ship without an Amazon overbox by default.
-In addition, eligible MCF and Buy with Prime SIPP shipments will receive a discount. See the SIPP for MCF help content for details.
-These updates support Amazon’s co</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1411,168 +1410,21 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
+          <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Seller News: March 2026</t>
+          <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services
- 96
- Updates to Seller Central workspaces, Upload Images, Product Opportunity explorer, and more.
- Our Seller Newsletter provides the most important policy, tool, and program updates from the past month. Stay informed about selling on Amazon.
- Introducing a new, AI-powered workspace
- You now have access to a dynamic canvas experience in Seller Central, where you can visualize data and key insights, explore scenarios, and take critical actions to grow your business. This integrated, AI-native workspace combines chat and visual elements to provide highly personalized and actionable insights. Read more .
- Upload Images now provides faster uploads and more flexibility
- We’ve enhanced the image upload process in Upload Images to make managing images for your product catalog faster and more flexible. Read more .
- Remove meltable FBA inventory by April 20
- To meet product quality standards, we won’t accept meltable inventory at our fulfillment centers between April 20, 2026, and September 28, 2026. Meltable inventory remaining in our fulfillment centers after April 20, may be marked unfillable and disposed of for a fee, starting May 1, 2026. Read more .
- Save and track pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Act today &amp; improve Sales on Excess Inventory</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Optional preview text
- Hello,
-We noticed you have a number of ASIN(s) that have excess levels of inventory. We are reaching out to inform you about multiple options to improve your Unit Sales on your aged and/or excess inventory in Amazon Fulfillment Centers. Our goal is to help you increase the sales on this excess inventory:
-X004QEYPRL, X004QFJQLF, X004MMFUYT, X004QEVV05, X004K6ILMZ
-We encourage you to take Amazon recommended actions such as Create Outlet deals, Sponsor Products Ad, to improve sell through of this excess inventory and potentially reduce your chances of incurring aged inventory fee.
- Outlet deals
- Amazon Outlet is a great place for customers to shop for overstock deals, which offers a selection of items, such as electronics, toys, beauty, and kitchen.
- Create Outlet Deal Today!
- Sponsored Product Ads
- Sponsored Products is a cost-per-click advertising solution that provides advertisers with a foundation of controls and visibility to help get their individual products discovered, and help generate sales from traffic sources in the Amazon store and on select premium apps and websites.
- Create Sponsored Products Ad Today!</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Seller News: March 2026</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services
- 96
- Stay informed about selling on Amazon.
- Our Seller Newsletter provides the most important policy, tool and programme updates from the past month.
- Introducing a new, AI-powered workspace
- You now have access to a dynamic canvas experience in Seller Central, where you can visualise data and key insights, explore scenarios and take critical actions to grow your business. This integrated, AI-native workspace combines chat and visual elements to provide highly personalised and actionable insights. Read more .
- Upload Images now provides faster uploads and more flexibility
- We’ve enhanced the image upload process in Upload Images to make managing images for your product catalogue faster and more flexible. Read more .
- Save and track product research with Product Opportunity Explorer
- Product Opportunity Explorer now includes a feature that helps you save and organise your research. You can identify profitable opportunities with low competition and save those promising product niches and ASINs with a single click. Read more .
- Account health tips for multiple selling accounts
- Our multiple-accounts policy allows you to operate one account per region unless you have a</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-04-02</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1593,39 +1445,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1649,39 +1501,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1704,39 +1556,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -1752,39 +1604,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -1798,40 +1650,40 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -1847,39 +1699,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1899,39 +1751,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -1945,39 +1797,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1997,39 +1849,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2050,39 +1902,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 04:02:47 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (uih6sNeVfd)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2102,39 +1954,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 20:32:33 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (DjHMcVqBnq)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2154,40 +2006,40 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:54:28 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 29.08 in an attempt to settle your Amazon.ca seller account balance.
@@ -2203,39 +2055,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 06:14:30 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (X8HTY1kPjb)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2261,39 +2113,88 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Tu pago está en camino</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 03/19/26 15:38 WET, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 74,59.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éxit</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -2308,39 +2209,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2364,39 +2265,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2410,39 +2311,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 14:57:34 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Negatieve saldoaanpassing voor al je accounts</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2459,39 +2360,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 13:38:27 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2511,39 +2412,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 15:38:46 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2560,39 +2461,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 16:06:24 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2616,39 +2517,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 14:48:41 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2668,39 +2569,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 14:12:31 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2720,87 +2621,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 24 Feb 2026 14:54:33 +0000</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Twoja płatność jest już w drodze</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>96
-Ten tytuł będzie wyświetlany na urządzeniach mobilnych
- Gratulujemy! Twoja płatność jest już w drodze, a środki powinny wkrótce do Ciebie dotrzeć.
- Próba wypłaty środków
-Gratulacje, Weihai EU! Twoja płatność jest już w drodze, a środki powinny do Ciebie dotrzeć w terminie od trzech do pięciu dni.
-Dnia 02/24/26 14:54 CET zainicjowaliśmy przelew na kwotę PLN
- 88.25 na konto powiązane z Twoją metodą płatności (rachunek bankowy o ostatnich cyfrach 229).
- Jeśli kwota jest mniejsza niż oczekiwana, oto kilka kwestii do wzięcia pod uwagę:
- Czy Twoje saldo jest niedostępne? Amazon może zatrzymać środki na pokrycie ewentualnych kosztów zwrotów towarów, roszczeń i obciążeń zwrotnych od kupujących. W takim przypadku saldo zamknięcia w raporcie płatności pokaże niedostępne saldo na zarezerwowaną w tym celu kwotę.
- Czy Twoja sprzedaż wystarczyła na pokrycie wszystkich opłat i zwrotów w tym okresie rozliczeniowym? Kwota płatności uwzględnia koszt działań sprzedażowych, opłaty za sprzedaż oraz opłaty za promocje i usługi. Aby lepiej zrozumieć wysokość salda zamknięcia, warto przeanalizować raport płatności, który znajdziesz w Seller Central w karcie „Raporty”.
-Więcej o raportach płatności w Sel</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -2819,39 +2672,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2869,39 +2722,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2923,39 +2776,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2978,39 +2831,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:20 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3029,39 +2882,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:09:14 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3080,39 +2933,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:43 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3132,39 +2985,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:31 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3184,39 +3037,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Vereisten voor naleving van je productvermeldingen aanpakken</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 Actie vereist: Belangrijke informatie over je productvermeldingen
@@ -3234,39 +3087,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3284,39 +3137,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Rispondi ai requisiti di conformità per le tue offerte</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 Azione richiesta: Informazioni importanti sulle sue offerte
@@ -3334,39 +3187,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:29 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3385,39 +3238,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 05:28:30 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3435,40 +3288,40 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 08:54:27 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3486,39 +3339,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 05:31:26 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3536,39 +3389,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 21:23:05 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3586,39 +3439,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:18:58 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3633,39 +3486,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 09:56:14 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3681,39 +3534,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 05:24:39 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3731,39 +3584,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 21:13:50 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3781,39 +3634,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:49 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3831,40 +3684,40 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 11:03:26 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 26/04/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 26/04/2026 to avoid shipping restrictions
@@ -3883,39 +3736,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 05:20:21 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3933,39 +3786,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Feb 2026 16:07:02 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Submit Product Safety Law compliance information for Saudi Arabia</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  You can now submit PSL compliance information through the listing workflow and Manage All Inventory.
@@ -3987,10 +3840,156 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
+Dear there,
+Thank you for being a valued member of the Amazon Multichannel Fulfillment (MCF) and Buy with Prime community. We are reaching again out to make sure you have seen that starting in April 2026, MCF and Buy with Prime will introduce two updates to how orders are packaged and shipped in the United States:
+Packing slips will no longer be included by default.
+Items already certified for the Ships in Product Packaging (SIPP) program on Amazon.com will ship without an Amazon overbox by default.
+In addition, eligible MCF and Buy with Prime SIPP shipments will receive a discount. See the SIPP for MCF help content for details.
+https://www2.amazonsupplychain.com/e/949422/ence-external-GVCFXDFYNCTFLTTQ/61b9cx/1372255659/h/xX050fPuJyuSx_HuFPheaHfGRXD19yafaiWekQ5-4Gg
+Packing slips will no longer be included by default.
+Items already certified for the Ships in Product Packaging (SIPP) program on Amazon.com will ship without an Amazon overbox by default.
+In addition, eligible MCF and Buy with Prime SIPP shipments will receive a discount. See the SIPP for MCF help content for details.
+These updates support Amazon’s co</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Seller News: March 2026</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services
+ 96
+ Updates to Seller Central workspaces, Upload Images, Product Opportunity explorer, and more.
+ Our Seller Newsletter provides the most important policy, tool, and program updates from the past month. Stay informed about selling on Amazon.
+ Introducing a new, AI-powered workspace
+ You now have access to a dynamic canvas experience in Seller Central, where you can visualize data and key insights, explore scenarios, and take critical actions to grow your business. This integrated, AI-native workspace combines chat and visual elements to provide highly personalized and actionable insights. Read more .
+ Upload Images now provides faster uploads and more flexibility
+ We’ve enhanced the image upload process in Upload Images to make managing images for your product catalog faster and more flexible. Read more .
+ Remove meltable FBA inventory by April 20
+ To meet product quality standards, we won’t accept meltable inventory at our fulfillment centers between April 20, 2026, and September 28, 2026. Meltable inventory remaining in our fulfillment centers after April 20, may be marked unfillable and disposed of for a fee, starting May 1, 2026. Read more .
+ Save and track pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Act today &amp; improve Sales on Excess Inventory</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Optional preview text
+ Hello,
+We noticed you have a number of ASIN(s) that have excess levels of inventory. We are reaching out to inform you about multiple options to improve your Unit Sales on your aged and/or excess inventory in Amazon Fulfillment Centers. Our goal is to help you increase the sales on this excess inventory:
+X004QEYPRL, X004QFJQLF, X004MMFUYT, X004QEVV05, X004K6ILMZ
+We encourage you to take Amazon recommended actions such as Create Outlet deals, Sponsor Products Ad, to improve sell through of this excess inventory and potentially reduce your chances of incurring aged inventory fee.
+ Outlet deals
+ Amazon Outlet is a great place for customers to shop for overstock deals, which offers a selection of items, such as electronics, toys, beauty, and kitchen.
+ Create Outlet Deal Today!
+ Sponsored Product Ads
+ Sponsored Products is a cost-per-click advertising solution that provides advertisers with a foundation of controls and visibility to help get their individual products discovered, and help generate sales from traffic sources in the Amazon store and on select premium apps and websites.
+ Create Sponsored Products Ad Today!</t>
+        </is>
+      </c>
+    </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4005,42 +4004,41 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 20:18:57 +0000</t>
+          <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Hantera efterlevnadskrav för dina produktposter</t>
+          <t>Seller News: March 2026</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>96
-Åtgärd krävs: Viktig information angående dina produktposter
- Vi kontaktar dig eftersom du har publicerat produkter som du måste skicka in dokument om överensstämmelse för.
- Produktposterna saknar dokument om överensstämmelse
- Hej!
- Vi kontaktar dig eftersom du har publicerat produkter för vilka du måste skicka in dokument om överensstämmelse. Klicka på Granska krav på överensstämmelse nedan om du vill visa listan med berörda produkter och skicka sedan in de dokument om överensstämmelse som krävs. Om du inte skickar in dokumenten senast det angivna förfallodatumet för respektive produkt i den här länken, så kan vi komma att ta bort de berörda produktposterna.
- Visa krav på överensstämmelse
- I tabellen nedan visas en av dina berörda produktposter som exempel. Klicka på Granska krav på överensstämmelse om du vill se alla dina berörda produktposter.
- SKU ASIN Status K6-KGRL-T8E4 B0DYTPRM8Z Riskerar borttagning
- Varför händer det här?
-Det här kravet hjälper till att säkerställa att produkterna är säkra för kunderna och överensstämmer med lokala lagar.
- Vad behöver jag göra om jag vill fortsätta att sälja de här produkterna?
-Klicka på Granska krav på överensstämmelse om du vill ha me</t>
+          <t>Amazon Services
+ 96
+ Stay informed about selling on Amazon.
+ Our Seller Newsletter provides the most important policy, tool and programme updates from the past month.
+ Introducing a new, AI-powered workspace
+ You now have access to a dynamic canvas experience in Seller Central, where you can visualise data and key insights, explore scenarios and take critical actions to grow your business. This integrated, AI-native workspace combines chat and visual elements to provide highly personalised and actionable insights. Read more .
+ Upload Images now provides faster uploads and more flexibility
+ We’ve enhanced the image upload process in Upload Images to make managing images for your product catalogue faster and more flexible. Read more .
+ Save and track product research with Product Opportunity Explorer
+ Product Opportunity Explorer now includes a feature that helps you save and organise your research. You can identify profitable opportunities with low competition and save those promising product niches and ASINs with a single click. Read more .
+ Account health tips for multiple selling accounts
+ Our multiple-accounts policy allows you to operate one account per region unless you have a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4055,172 +4053,21 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 17:12:51 +0000</t>
+          <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Submit product compliance documents to avoid listing removal</t>
+          <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product compliance documents to avoid listing removal
- Hello Weihai US,
- Your listings are at risk of removal due to missing Safety Data Sheets. Submit the required documentation by 2026-04-09 to continue selling these products. You can find examples of your at-risk listings at the bottom of this email.
- Why is this happening?
- We are taking this action because we identified hazardous products in your catalog that require Safety Data Sheets (SDS). These documents are required by law and provide critical safety information about chemical products, including proper handling, storage, and emergency procedures. This helps ensure the safety of our customers, employees, and anyone who handles these products.
- To learn more, visit our Requirements and FAQ for the sale of chemicals .
- How do I continue to sell the affected products?
- To avoid listing removal and continue selling these products, upload the Safety Data Sheets (SDS) for each of the impacted products. Click the “View Compliance Requirements” button below to see all affected listings.
- View Compliance Requirements
- What was impacted?
- Reason
- At-risk sales
- Roaxkois Paint Your Own Mug Set, Mother's Day Pottery Kit In</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 23 Feb 2026 17:10:23 +0000</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>Submit product compliance documents to avoid listing removal</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product compliance documents to avoid listing removal
- Hello Weihai CA,
- Your listings are at risk of removal due to missing Safety Data Sheets. Submit the required documentation by 2026-04-09 to continue selling these products. You can find examples of your at-risk listings at the bottom of this email.
- Why is this happening?
- We are taking this action because we identified hazardous products in your catalogue that require Safety Data Sheets (SDS). These documents are required by law and provide critical safety information about chemical products, including proper handling, storage and emergency procedures. This helps ensure the safety of our customers, employees and anyone who handles these products.
- To learn more, visit our Requirements and FAQ for the sale of chemicals .
- How do I continue to sell the affected products?
- To avoid listing removal and continue selling these products, upload the Safety Data Sheets (SDS) for each of the impacted products. Click the “View Compliance Requirements” button below to see all affected listings.
- View Compliance Requirements
- What was impacted?
- Reason
- At-risk sales
- Paint Your Own Mug Set, Mother's Day Pottery Kit Includes Mu</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 23 Feb 2026 16:27:54 +0000</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>Notificaciones automáticas de Amazon Seller Central (favor de no responder a este mensaje) &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>Aborda los requisitos de cumplimiento para los listados</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>96
-Acción requerida: Información importante sobre tus listados de productos
- Nos ponemos en contacto contigo ya que has publicado productos que requieren nos envíes documentos de cumplimiento normativo.
- A los listados de productos les faltan documentos obligatorios de cumplimiento normativo
- Hola:
- Nos comunicamos contigo porque publicaste productos que requieren que envíes documentos de cumplimiento normativo. Haz clic en “Revisar requisitos de cumplimiento normativo” a continuación para consultar la lista de productos afectados y enviar los documentos de cumplimiento normativo obligatorios. Si no envías la documentación antes de la fecha de vencimiento indicada para cada producto en este enlace, es posible que se eliminen los listados afectados.
- Revisar requisitos de cumplimiento normativo
- La siguiente tabla contiene una muestra de los listados afectados. Haz clic en “Revisar requisitos de cumplimiento normativo” para consultar todos los listados afectados.
- SKU ASIN Estado del listado 7N-0PZT-LEBX B0FCDRNTT8 Listados en riesgo de retiro
- ¿A qué se debe?
-Este requisito ayuda a garantizar que los productos cumplan con las leyes locales y que sean seguros para los clientes.
- ¿Có</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>A Amazon enviou os itens vendidos</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -4244,39 +4091,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4291,39 +4138,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -4339,39 +4186,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4388,40 +4235,40 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -4437,39 +4284,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -4489,39 +4336,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -4537,40 +4384,40 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4586,39 +4433,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4635,39 +4482,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4686,39 +4533,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -4736,39 +4583,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
@@ -4780,39 +4627,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4824,39 +4671,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -4868,39 +4715,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4912,39 +4759,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4956,39 +4803,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
@@ -5000,39 +4847,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5044,39 +4891,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5088,39 +4935,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -5138,39 +4985,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  尊敬的 Weihai EU：
@@ -5213,39 +5060,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -5262,40 +5109,40 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -5313,39 +5160,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -5363,39 +5210,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5407,39 +5254,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5451,39 +5298,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5502,39 +5349,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5546,39 +5393,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5590,39 +5437,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5634,39 +5481,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5678,39 +5525,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5722,39 +5569,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5766,39 +5613,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5810,39 +5657,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5854,39 +5701,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5898,40 +5745,40 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5950,39 +5797,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5994,40 +5841,40 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
  2/2026</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
 Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
@@ -6039,39 +5886,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6083,39 +5930,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:32:33 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Fulfillment by Amazon Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6134,39 +5981,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:13:19 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6178,39 +6025,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:56:47 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6229,39 +6076,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:29:22 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 2 2026</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 2 i rok 2026.
@@ -6273,39 +6120,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 11:10:20 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6321,40 +6168,40 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:11:42 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6372,39 +6219,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:08:11 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -6422,39 +6269,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:32 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Spełnij wymogi zgodności dotyczące Twoich ofert</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
 Wymagane działanie: Ważna informacja dotycząca Twoich ofert produktów
@@ -6470,39 +6317,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:29 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento de tus listings</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
 Toma medidas: Información importante sobre tus listings de producto
@@ -6520,39 +6367,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:47 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -6593,39 +6440,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:22 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -6643,40 +6490,40 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:12:51 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -6694,39 +6541,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:28 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6743,39 +6590,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:09:31 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6793,39 +6640,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 11:10:25 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6843,39 +6690,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 00:58:56 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>最后机会：请在3月9日前提报春季促销日的促销</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>3月9日前提报春季促销日促销
 尊敬的卖家，
@@ -6890,39 +6737,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 21:40:34 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6936,39 +6783,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 11:10:30 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6984,39 +6831,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:13:10 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 60 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -7032,39 +6879,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:09:55 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 60 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7081,40 +6928,40 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:07:47 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 60 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7130,39 +6977,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 18:30:15 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para marzo</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para marzo
@@ -7191,39 +7038,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:58 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -7240,40 +7087,40 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:56 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -7290,39 +7137,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:35 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7337,40 +7184,40 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:40 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7385,39 +7232,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:31 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -7432,39 +7279,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:23 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -7479,39 +7326,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 15:01:07 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7526,39 +7373,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 10:49:26 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -7586,85 +7433,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 23 Feb 2026 17:09:03 +0000</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>96
- Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados
- Hola, Weihai MX:
- Tus listados están en riesgo de ser retirados debido a que faltan las fichas de datos de seguridad (FDS). Envía la documentación obligatoria a más tardar el 2026-04-09 para seguir vendiendo estos productos. En la parte inferior de este correo electrónico, encontrarás ejemplos de listados en riesgo.
- ¿A qué se debe?
- Tomamos esta medida porque identificamos productos peligrosos en tu catálogo que requieren fichas de datos de seguridad (FDS). Estos documentos son obligatorios por ley y proporcionan información de seguridad importante sobre productos químicos, incluidos procedimientos de manipulación, almacenamiento y emergencia adecuados. Esto ayuda a garantizar la seguridad de nuestros clientes, empleados y cualquier persona que manipule estos productos.
- Para más información, consulta los Requisitos y preguntas frecuentes para la venta de productos químicos .
- ¿Cómo puedo seguir vendiendo los productos afectados?
- Si quieres evitar el retiro de listados y seguir vendiendo estos productos, carga la ficha de datos de seguridad (FDS) de cada uno de los productos afect</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7687,39 +7488,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7741,39 +7542,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:58:29 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7796,39 +7597,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:29:25 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7851,39 +7652,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 07:49:31 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>New removal fees for KSA apply starting March 30</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  Effective March 30, 2026, removal fees will apply in the Kingdom of Saudi Arabia (KSA) for removals you initiate.
@@ -7909,39 +7710,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 13:57:30 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-12</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7963,39 +7764,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 12:08:33 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8019,40 +7820,40 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8071,40 +7872,40 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8122,39 +7923,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -8168,39 +7969,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
@@ -8218,39 +8019,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
 Wijziging in geschiktheid voor opties voor premiumverzending
@@ -8267,39 +8068,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 12:16:06 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Behörighet att ändra alternativ för Premiumfrakt</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
 Behörighet att ändra alternativ för Premiumfrakt
@@ -8317,40 +8118,40 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 05:10:16 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Premium Shipping option eligibility suspended due to program
  requirement violation</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
 Premium Shipping option eligibility suspended due to program requirement violation
@@ -8369,39 +8170,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:12 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (Ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Répondez aux exigences de conformité pour vos mises en vente</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
 Action requise : informations importantes concernant vos offres
@@ -8417,39 +8218,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Sun, 1 Mar 2026 00:16:30 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>View your US Q1-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q1-2026
@@ -8479,40 +8280,40 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:10:48 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8531,40 +8332,40 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:06:07 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8582,39 +8383,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 01:35:07 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Upload proof of insurance and explore new best practices guide</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Upload proof of commercial liability insurance by March 30, 2026. Review our new best practices guide for mainland China-based sellers to help you avoid common coverage gaps and policy issues.

--- a/important_mails_2026-03-26.xlsx
+++ b/important_mails_2026-03-26.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -549,21 +549,70 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
+          <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Action Required: Website Suppressed ASINs</t>
+          <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>96
+ We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
+ Hello,
+ According to rules for online stores issued by the State Council of China (Decree No. 810), we are required to provide information on China-based sellers to the Chinese tax authority on a quarterly basis.
+ We’ve submitted your quarterly tax report covering October to December 2025, which includes your identity information, number of transactions, revenue, and commission and service fees.
+ Download your quarterly report (link active for seven days)
+This report is provided for your reference only, no action is required.
+ Based on your feedback, we’ve also provided a more granular order-level report that displays your quarterly information by transaction.
+ Download your order-level report (link active for seven days)
+Note: Variation between the data in these reports and your payment and Amazon VAT transactions report is expected. Each report uses distinct methodology and serves a different purpose.
+ We’ll continue to provide you with quarterly updates on data shared with the Chinese tax authority.
+ For more information, go to China tax information reporti</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Action Required: Website Suppressed ASINs</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -578,39 +627,87 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
+ Dzień dobry,
+ zgodnie z zasadami dotyczącymi sklepów internetowych wydanymi przez Radę Państwa Chin (dekret nr 810) jesteśmy zobowiązani do przekazywania informacji o sprzedawcach z siedzibą w Chinach tamtejszemu organowi podatkowemu w cyklach kwartalnych.
+ Przesłaliśmy Twój kwartalny raport podatkowy za okres od października do grudnia 2025 r., który zawiera Twoje dane identyfikacyjne, liczbę transakcji, przychody oraz prowizje i opłaty za usługi.
+ Pobierz swój kwartalny raport (link aktywny przez siedem dni)
+Raport jest przeznaczony wyłącznie do wglądu, nie jest wymagane żadne działanie.
+ Na podstawie Twojej opinii udostępniliśmy też bardziej szczegółowy raport na poziomie zamówienia, który przedstawia informacje kwartalne z podziałem na transakcje.
+ Pobierz raport na poziomie zamówienia (link aktywny przez siedem dni)
+Uwaga: mogą wystąpić różnice między danymi w tych raportach a raportem o płatnościach i raportem Amazon o transakcjach podlegających VAT. Każdy raport korzysta z odrębnej metodologii i służy do innego celu.
+ Będziemy Ci nadal przekazywać kwartalne</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -630,39 +727,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -688,39 +785,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -736,39 +833,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -789,39 +886,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -836,39 +933,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -887,40 +984,40 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -939,39 +1036,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -981,39 +1078,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1031,39 +1128,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -1079,39 +1176,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1126,39 +1223,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -1173,39 +1270,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -1226,40 +1323,40 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -1274,39 +1371,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -1327,39 +1424,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -1392,39 +1489,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1445,39 +1542,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1501,39 +1598,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1556,39 +1653,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -1604,39 +1701,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -1650,40 +1747,40 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -1699,39 +1796,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1751,39 +1848,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -1797,39 +1894,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1849,39 +1946,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1902,39 +1999,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 04:02:47 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (uih6sNeVfd)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1954,39 +2051,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 20:32:33 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (DjHMcVqBnq)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2006,40 +2103,40 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:54:28 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 29.08 in an attempt to settle your Amazon.ca seller account balance.
@@ -2055,39 +2152,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 06:14:30 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (X8HTY1kPjb)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2113,39 +2210,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2162,39 +2259,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -2209,39 +2306,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2265,39 +2362,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2311,39 +2408,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 14:57:34 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Negatieve saldoaanpassing voor al je accounts</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2360,39 +2457,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 13:38:27 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2412,39 +2509,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 15:38:46 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2461,39 +2558,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 16:06:24 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2517,39 +2614,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 14:48:41 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2569,39 +2666,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 14:12:31 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2621,39 +2718,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -2672,39 +2769,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2722,39 +2819,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2776,39 +2873,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2831,39 +2928,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:20 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2882,39 +2979,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:09:14 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2933,39 +3030,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:43 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -2985,39 +3082,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:31 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3037,39 +3134,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Vereisten voor naleving van je productvermeldingen aanpakken</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 Actie vereist: Belangrijke informatie over je productvermeldingen
@@ -3087,39 +3184,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3137,39 +3234,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Rispondi ai requisiti di conformità per le tue offerte</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 Azione richiesta: Informazioni importanti sulle sue offerte
@@ -3187,39 +3284,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:29 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3238,39 +3335,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 05:28:30 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3288,40 +3385,40 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 08:54:27 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3339,39 +3436,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 05:31:26 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3389,39 +3486,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 21:23:05 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3439,39 +3536,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:18:58 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3486,39 +3583,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 09:56:14 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3534,39 +3631,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 05:24:39 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3584,39 +3681,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 21:13:50 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3634,39 +3731,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:49 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3684,40 +3781,40 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 11:03:26 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 26/04/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 26/04/2026 to avoid shipping restrictions
@@ -3736,39 +3833,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 05:20:21 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3786,39 +3883,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Feb 2026 16:07:02 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Submit Product Safety Law compliance information for Saudi Arabia</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  You can now submit PSL compliance information through the listing workflow and Manage All Inventory.
@@ -3840,39 +3937,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -3888,39 +3985,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3936,39 +4033,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3986,39 +4083,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4035,39 +4132,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -4091,39 +4188,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4138,39 +4235,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -4186,39 +4283,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4235,40 +4332,40 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -4284,39 +4381,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -4336,39 +4433,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -4384,40 +4481,40 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4433,39 +4530,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4482,39 +4579,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4533,39 +4630,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -4583,39 +4680,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
@@ -4627,39 +4724,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4671,39 +4768,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -4715,39 +4812,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4759,39 +4856,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4803,39 +4900,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
@@ -4847,39 +4944,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4891,39 +4988,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4935,39 +5032,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -4985,39 +5082,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  尊敬的 Weihai EU：
@@ -5060,39 +5157,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -5109,40 +5206,40 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -5160,39 +5257,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -5210,39 +5307,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5254,39 +5351,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5298,39 +5395,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5349,39 +5446,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5393,39 +5490,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5437,39 +5534,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5481,39 +5578,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5525,39 +5622,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5569,39 +5666,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5613,39 +5710,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5657,39 +5754,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5701,39 +5798,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5745,40 +5842,40 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5797,39 +5894,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5841,40 +5938,40 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
  2/2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
 Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
@@ -5886,39 +5983,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5930,39 +6027,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:32:33 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Fulfillment by Amazon Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5981,39 +6078,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:13:19 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6025,39 +6122,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:56:47 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6076,39 +6173,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:29:22 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 2 2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 2 i rok 2026.
@@ -6120,39 +6217,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 11:10:20 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6168,40 +6265,40 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:11:42 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6219,39 +6316,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:08:11 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -6269,39 +6366,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:32 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Spełnij wymogi zgodności dotyczące Twoich ofert</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
 Wymagane działanie: Ważna informacja dotycząca Twoich ofert produktów
@@ -6317,39 +6414,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:29 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento de tus listings</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 Toma medidas: Información importante sobre tus listings de producto
@@ -6367,39 +6464,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:47 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -6440,39 +6537,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:22 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -6490,40 +6587,40 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:12:51 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -6541,39 +6638,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:28 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6590,39 +6687,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:09:31 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6640,39 +6737,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 11:10:25 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6690,39 +6787,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 00:58:56 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>最后机会：请在3月9日前提报春季促销日的促销</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>3月9日前提报春季促销日促销
 尊敬的卖家，
@@ -6737,39 +6834,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 21:40:34 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6783,39 +6880,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 11:10:30 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6831,39 +6928,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:13:10 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 60 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -6879,39 +6976,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:09:55 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 60 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6928,40 +7025,40 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:07:47 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 60 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6977,39 +7074,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 18:30:15 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para marzo</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para marzo
@@ -7038,39 +7135,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:58 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -7087,40 +7184,40 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:56 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -7137,39 +7234,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:35 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7184,40 +7281,40 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:40 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7232,39 +7329,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:31 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -7279,39 +7376,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:23 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -7326,39 +7423,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 15:01:07 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7373,39 +7470,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 10:49:26 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -7433,39 +7530,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7488,39 +7585,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7542,39 +7639,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:58:29 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7597,39 +7694,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:29:25 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7652,39 +7749,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 07:49:31 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>New removal fees for KSA apply starting March 30</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  Effective March 30, 2026, removal fees will apply in the Kingdom of Saudi Arabia (KSA) for removals you initiate.
@@ -7710,39 +7807,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 13:57:30 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-12</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7764,39 +7861,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 12:08:33 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7820,40 +7917,40 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7872,40 +7969,40 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7923,39 +8020,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -7969,39 +8066,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
@@ -8019,39 +8116,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
 Wijziging in geschiktheid voor opties voor premiumverzending
@@ -8068,39 +8165,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 12:16:06 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Behörighet att ändra alternativ för Premiumfrakt</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
 Behörighet att ändra alternativ för Premiumfrakt
@@ -8118,40 +8215,40 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 05:10:16 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Premium Shipping option eligibility suspended due to program
  requirement violation</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
 Premium Shipping option eligibility suspended due to program requirement violation
@@ -8170,39 +8267,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:12 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (Ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Répondez aux exigences de conformité pour vos mises en vente</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
 Action requise : informations importantes concernant vos offres
@@ -8218,39 +8315,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Sun, 1 Mar 2026 00:16:30 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>View your US Q1-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q1-2026
@@ -8280,40 +8377,40 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:10:48 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8332,40 +8429,40 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:06:07 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8383,39 +8480,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 01:35:07 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Upload proof of insurance and explore new best practices guide</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>96
  Upload proof of commercial liability insurance by March 30, 2026. Review our new best practices guide for mainland China-based sellers to help you avoid common coverage gaps and policy issues.
